--- a/Employee_Reports_wi52/Mohamed Mufaris Mohamed Jameel Q0532.xlsx
+++ b/Employee_Reports_wi52/Mohamed Mufaris Mohamed Jameel Q0532.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-96</v>
+        <v>-104</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-322</v>
+        <v>-330</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-440</v>
+        <v>-448</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-517</v>
+        <v>-525</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1057,11 +1057,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1072,41 +1072,41 @@
       <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1143,11 +1143,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1192,11 +1192,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1229,11 +1229,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1244,41 +1244,41 @@
       <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2024</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
